--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1513,43 +1513,403 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="18" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+    <row r="14" ht="113" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>04-10-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Definir el flujo del profesional según el mockup del Product Owner: al elegir la cuenta profesional no completa datos personales, objetivos ni salud; completa su ficha profesional y entra a un espacio propio con Inicio (saludo, tareas, accesos rápidos y resumen semanal), Agenda, Perfil profesional con pestañas y las secciones Clientes, Mensajes, Reportes y Configuración como «Próximamente». Se implementó en los PR #12 y #13.</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-02, FS-HU-04</t>
+        </is>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>CU-02, CU-04</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="83" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Mostrar el clima en el Inicio del profesional: el backend consulta Open-Meteo con las coordenadas de la ficha (redondeadas), guarda la respuesta 30 minutos y, si no hay ficha, usa Santiago. Endpoint GET /api/clima solo para profesionales (decisión D26 del DAS).</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-04</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>CU-04</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="113" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Ajustar el menú del usuario según el mockup del Asistente de IA: «Historial de chats» sale del menú lateral y pasará a estar dentro del Asistente (FS-HU-07); se agrega «Comidas» como «Próximamente» (FS-HU-09 y FS-HU-10, macronutrientes solo de lo consumido) y se quitan las farmacias del menú, los accesos rápidos, la portada y el Inicio (quedan centros de salud y gimnasios).</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-07, FS-HU-10, FS-HU-20, FS-HU-21</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>CU-01, CU-05, CU-06</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="113" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>08-10-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Corregir el cambio SC-08: el tipo de cuenta se elige una sola vez en una pantalla propia (/elegir-perfil) después del registro o del ingreso con Google, y no en el paso 1 del asistente, que vuelve a tener 4 pasos. Cambiarlo después lo hace un administrador (409 si ya se eligió). El profesional no accede a las pantallas ni a la API del usuario (decisión D25 del DAS, que reemplaza a D21).</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-02, FS-HU-16, FS-HU-17</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>CU-01, CU-02</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="113" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>10-10-2026</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Ampliar FS-HU-12 con el panel del administrador según el mockup del Product Owner (Dashboard, Profesionales, Verificaciones, Usuarios y Reportes; Configuración y Contenido quedan fuera), con solicitudes y documentos de verificación. Como Luis Méndez la implementó en el Sprint 3 (PR #15, #19 y #20), el 12-10-2026 se reubicó del Sprint 5 al Sprint 3 y el Product Owner la aceptó con una observación.</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-12</t>
+        </is>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>CU-07</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K18" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="98" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>12-10-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Limitar a una reserva activa (pendiente o confirmada) de un horario futuro por usuario con cada profesional; las citas que ya pasaron no cuentan. Si no se cumple, la API responde 409 con el motivo y la ficha avisa antes de escribir el mensaje. Se agregó el escenario 4 a FS-HU-14 y se implementó en el PR #22 (defecto 26 corregido).</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-14</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 03-10-2026.</t>
         </is>
@@ -1557,11 +1917,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -1885,7 +1885,68 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1"/>
+    <row r="20" ht="128" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Nicolás Silva / Desarrollador frontend</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Reemplazar Google Maps por MapLibre GL JS 5.24.0 con teselas de OpenFreeMap (datos de OpenStreetMap) en la vista Mapa de FS-HU-06, porque Google Maps exige una clave con facturación y eso bloqueaba CP-078. Es gratuito y no requiere clave, cuenta ni tarjeta; el SDK se descarga solo al abrir la vista, con versión fija y huella SRI, y la lista sigue disponible si el mapa falla. PR #27, fusionado el 15-10-2026; DAS 1.23 (D31 reemplaza a D8).</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-06</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
+        <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 3 (semanas 9 y 10)</t>
+        </is>
+      </c>
+      <c r="K20" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1947,42 +1947,105 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Mejorar la respuesta y el movimiento de la interfaz sin cambiar funciones: lo que se presiona se achica apenas; los efectos al pasar el mouse solo aplican con mouse; el menú lateral y la hoja de filtros del celular se abren con curva de cajón, con fondo que se funde y sin desplazar la página de fondo; los menús de la cuenta y de notificaciones crecen desde su botón; entradas breves en Elegir perfil y en el asistente de perfil; el corazón de favoritos late al marcarlo; se respeta la preferencia «reducir movimiento» y en el celular los campos usan 16 px y las pantallas 100dvh. Incluye la corrección de los defectos 30 a 34 (CP-081 a CP-087). Sin dependencias nuevas.</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-02, FS-HU-13, FS-HU-14, FS-HU-21 a FS-HU-23</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>CU-02, CU-03, CU-08, CU-09</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 03-10-2026.</t>
-        </is>
-      </c>
-    </row>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2009,43 +2009,167 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+    <row r="22" ht="165" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>SC-20</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Rediseñar la reserva de FS-HU-14 según el flujo de calendario que aportó el Product Owner: resumen del profesional (duración, modalidad y hora de Chile), calendario del mes con los días que tienen horas, horas del día con «Confirmar» en la misma fila, mensaje obligatorio de 10 a 500 caracteres en el paso de confirmar y pantalla «Solicitud enviada» con el estado «Pendiente de confirmación». «Agregar al calendario» descarga un archivo .ics generado en el navegador: no hay integración con calendarios externos, que siguen fuera del alcance. Se omitió «Agendar otra» del modelo por el límite de una reserva activa con cada profesional. Sin cambios en la API ni en la base de datos (CP-088 a CP-091).</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-14</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="135" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>SC-21</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Reemplazar el campo de fecha de «Publicar un horario» por el mismo calendario de la reserva (SC-20): abre en el mes actual, no deja elegir días pasados y marca los días que ya tienen horarios publicados; al lado se eligen la hora de inicio y la de término, con una duración rápida (30 min, 45 min, 1 h y 1 h 30 min) y la lista de lo ya publicado ese día. «Editar horario» lleva al formulario en el mes del horario. Sin cambios en la API ni en la base de datos (CP-092 y CP-093).</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-13</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="29" t="inlineStr">
         <is>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="29"/>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A28:L28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2133,43 +2133,229 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>SC-22</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Mostrar en la ventana de cada marcador del mapa el detalle del profesional: especialidad y modalidad, si está verificado, el lugar de atención (la dirección del establecimiento cuando la ficha tiene uno; si no, la comuna y un enlace «Cómo llegar» al punto exacto, porque la ficha no guarda una dirección propia) y su próxima hora disponible, con enlace a la ficha para reservar. La selección se registra al abrirse la ventana, también con el teclado (corrige el defecto 28). Sin cambios en la API ni en los datos (CP-095 y CP-096).</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-06</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K24" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="165" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>SC-23</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Convertir el buscador «¿Qué necesitas hoy?» del Inicio, que solo buscaba profesionales, en un buscador para recorrer la aplicación: mientras se escribe sugiere secciones por su nombre o por palabras relacionadas (por ejemplo «chat» o «ia» → Asistente IA; «reservas» → Mis citas; «salud» → Mi perfil y Centros de salud), especialidades del directorio («Ver profesionales de Nutrición») y, al final, siempre buscar el texto en profesionales. Enter abre la sugerencia marcada, las flechas la cambian y Escape cierra; accesible para lector de pantalla. Las secciones salen de la misma lista que el menú. Sin cambios en la API ni en los datos (CP-097 y CP-098).</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-21</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>CU-01, CU-03</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="180" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>SC-24</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>19-10-2026</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Agregar a la ficha del profesional una dirección de atención propia (columna profesionales.direccion, VARCHAR(150), nula), obligatoria si atiende presencial o de ambas formas y opcional si atiende solo online, y mostrarla en la ficha pública, en la ventana del marcador del mapa, en el perfil del profesional y en el lugar de la reserva (antes solo existía la del establecimiento, en 4 de 12 fichas). Además, las coordenadas de la ficha deben estar en Chile, con el mismo recuadro que limita el mapa, para que no se repita el defecto 35. Migración aditiva; DAS 1.24 (D32) y diagramas 02, 03 y 04 actualizados (CP-099 y CP-100). Las fichas presenciales existentes deberán agregar su dirección la próxima vez que se editen.</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-04, FS-HU-06</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>CU-03, CU-04</t>
+        </is>
+      </c>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K26" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
+    <row r="32"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A28:L28"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A31:L31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2319,42 +2319,104 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="27" ht="195" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>SC-25</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>21-10-2026</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Cambiar el proveedor del asistente IA de la API de Claude (de pago) a Groq, con plan gratuito y API compatible con OpenAI, mediante un cliente genérico configurable por .env (IA_URL_BASE, IA_MODELO e IA_API_KEY), para no depender de un pago durante el semestre. El asistente (FS-HU-07) guarda conversaciones y mensajes, limita a 30 los mensajes de cada usuario por día (tabla uso_asistente), envía al proveedor solo las instrucciones y los últimos 10 mensajes (sin perfil ni datos de salud) y agrega los avisos del SAMU (131) o *4141 ante señales de riesgo. Sin clave responde en modo de prueba. Migración aditiva 20261021120000_asistente_ia; DAS 1.25 (D33 reemplaza a D7) y diagramas 01, 02, 03, 04, 07, 08 y 14 actualizados (CP-103 a CP-109). FS-HU-08 usará el mismo proveedor.</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-07, FS-HU-08</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>CU-05</t>
+        </is>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="29" t="inlineStr">
         <is>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
+    <row r="33"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A28:L28"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A31:L31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2381,40 +2381,102 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="28" ht="180" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>SC-26</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>22-10-2026</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Que el asistente IA indique llamar al SAMU (131) solo ante situaciones críticas (por ejemplo, un hueso roto, dificultad para respirar o dolor fuerte en el pecho) y no en molestias leves como agujetas, una torcedura leve o un dolor muscular, y quitar el «En una emergencia, llama al 131» fijo del pie del chat. Se ajustaron las instrucciones del modelo y la red de seguridad del backend (solo frases críticas); el *4141 ante señales de riesgo suicida se mantiene. Con Groq real, las molestias leves que mencionaban el 131 bajaron de 3 de 8 a 0 de 8 y las situaciones críticas siguen en 5 de 5 (CP-113). DAS 1.26.</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-07</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>CU-05</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
         <is>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
+    <row r="34"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A31:L31"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2443,43 +2443,105 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="29" ht="225" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>SC-27</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>22-10-2026</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Juntar la lista y el mapa en Profesionales según el mockup del Product Owner, solo con los datos que ya existen: la lista a la izquierda y el mapa fijo a la derecha (en celular, el mapa arriba de la lista), en vez de alternar con los botones Lista y Mapa. Elegir un marcador muestra el detalle del profesional bajo el mapa (antes, una ventana sobre el marcador, SC-22) y marca su tarjeta; «Ver en el mapa» en cada tarjeta hace lo mismo desde la lista; pasar el mouse por una tarjeta resalta su marcador y al revés. Se agregan accesos rápidos por especialidad («+2 más»), los filtros pasan a una barra horizontal y el mapa se puede ocultar (?mapa=oculto). Quedan fuera del alcance, por no existir los datos: precio, etiquetas, boleta o factura, horario semanal, fotos y la leyenda de centros, gimnasios y farmacias. Sin cambios en la API ni en los datos (CP-115 a CP-119). Corrige además el defecto 37. DAS 1.27 (D35).</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-06, FS-HU-22</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="29" t="inlineStr">
         <is>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
           <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
+    <row r="35"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A34:L34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2505,43 +2505,105 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="30" ht="225" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>SC-28</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>24-10-2026</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Quitar los campos de latitud y longitud de la ficha del profesional, porque una persona común no sabe obtener coordenadas: el profesional escribe solo su comuna y su dirección, el backend las busca en Nominatim (el buscador de direcciones de OpenStreetMap, gratuito y sin clave) y el recuadro «Vista previa del mapa de ubicación» pasa a ser un mapa real con el marcador del lugar encontrado. Si no quedó exacto (por ejemplo, encontró la calle pero no el número), el profesional arrastra el marcador, hace clic en el mapa o lo mueve con las flechas del teclado. Nueva ruta GET /api/profesionales/mi-ficha/ubicacion (solo rol profesional), con una consulta por segundo, caché de 24 horas e identificación de la aplicación, como exige la política de uso de Nominatim. Sin cambios en la base de datos: la ficha sigue guardando latitud y longitud, y la API las sigue validando dentro de Chile. Retoma la alternativa que D32 había descartado (geocodificar la dirección). DAS 1.28 (D36) y diagramas 07 y 08 actualizados (CP-123 a CP-125).</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-04</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="inlineStr">
+        <is>
+          <t>CU-04</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+          <t>• Solicitante: el cliente del proyecto está representado por el Product Owner; también se registran los cambios pedidos por el docente o propuestos por un integrante del equipo.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 19-10-2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
+          <t>• Requerimiento relacionado: FitSearch trabaja con Scrum y sus requerimientos funcionales son las historias de usuario del Product Backlog, por eso se indica el ID de la historia (FS-HU-N°). Los casos de uso (CU-N°) son los del Documento de Arquitectura del Sistema (DAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 24-10-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A31:L31"/>
     <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:L35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="4294967294" verticalDpi="0"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2567,7 +2567,68 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
+    <row r="31" ht="225" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>SC-29</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Luis Méndez / Scrum Master (propuesta del equipo); aceptada por Rodrigo Cárcamo Rojas / Product Owner</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>25-10-2026</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Rediseñar la portada pública y el Inicio del usuario sin cambiar funciones (PR #33 de Luis Méndez, aprobado por el PO el 26-10-2026): la portada abre con una escena ilustrativa de un centro de bienestar cuyas puertas se abren al bajar y presenta bienvenida, especialidades y asistente IA (con movimiento reducido o poca altura de pantalla, todo en flujo normal), encabezado y paneles translúcidos, buscador por especialidad y comuna que conserva los filtros al pasar por el inicio de sesión, y fotografías ilustrativas generadas para el proyecto (no son profesionales ni pacientes reales). El Inicio agrega saludo, fotografía, tarjetas por especialidad y destaca el asistente; perfil, objetivos, citas, destacados y favoritos siguen con datos reales y lo no implementado mantiene «Próximamente». En la revisión se corrigieron los defectos 40 (tiradores de las puertas sobre el texto) y 41 (el h1 y el aviso de sesión quedaban ocultos al avanzar la escena). Sin cambios en la API, la base de datos ni la arquitectura (CP-126 a CP-130).</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>FS-HU-20, FS-HU-21</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>CU-01, CU-03</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>Fase 2 – Sprint 4 (semanas 11 y 12)</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="inlineStr">
+        <is>
+          <t>Aceptado</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
@@ -2592,11 +2653,10 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 24-10-2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+          <t>• El detalle y la justificación de cada cambio están en la sección 3 de la Guía 2.4, en el historial de versiones del DAS y en los comentarios del Product Backlog. Actualizado al 26-10-2026.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A33:L33"/>
